--- a/dictionary/variable_dictionary.xlsx
+++ b/dictionary/variable_dictionary.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
   <si>
     <t xml:space="preserve">Variable Name</t>
   </si>
@@ -72,36 +72,36 @@
     <t xml:space="preserve">id_dom</t>
   </si>
   <si>
+    <t xml:space="preserve">Project-derived</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificador do domicílio, tornado globalmente único como string composta "&lt;V1014&gt;_&lt;id&gt;" (derivado do id_dom do datazoom, que é único apenas DENTRO de cada grupo de rotação V1014). Usado como variável de clusterização nas especificações principais. Ver nota de correção do build no CLAUDE.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Household identifier, made globally unique as the composite string "&lt;V1014&gt;_&lt;id&gt;" (derived from datazoom's id_dom, which is unique only WITHIN each V1014 rotation group). Clustering variable in the main specifications. See the build fix note in CLAUDE.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Character composite "&lt;V1014&gt;_&lt;id&gt;", globally unique across panels. E.g. '10_1'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_panel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificador de painel para uso em efeitos fixos (feols(... | id_panel)). Igual a id_rs3 quando o pareamento foi bem-sucedido (panel_matched==1); quando id_rs3 é NA, recebe um ID único por linha (prefixo 'unmatched_'), evitando que indivíduos diferentes não pareados sejam agrupados no mesmo efeito fixo espúrio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel identifier for use in fixed effects (feols(... | id_panel)). Equal to id_rs3 when matching succeeded (panel_matched==1); when id_rs3 is NA, assigned a unique row-level ID (prefix 'unmatched_'), so different unmatched individuals are not lumped into the same spurious fixed effect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">String. Equals id_rs3 for matched rows; 'unmatched_&lt;row number&gt;' for unmatched rows. Always non-missing — safe to use directly as the FE variable in feols().</t>
+  </si>
+  <si>
+    <t xml:space="preserve">panel_matched</t>
+  </si>
+  <si>
     <t xml:space="preserve">integer</t>
   </si>
   <si>
-    <t xml:space="preserve">Identificador do domicílio. Único dentro de cada grupo de rotação V1014.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Household identifier. Unique within each V1014 panel rotation group.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integer. Unique within V1014 group.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id_panel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project-derived</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identificador de painel para uso em efeitos fixos (feols(... | id_panel)). Igual a id_rs3 quando o pareamento foi bem-sucedido (panel_matched==1); quando id_rs3 é NA, recebe um ID único por linha (prefixo 'unmatched_'), evitando que indivíduos diferentes não pareados sejam agrupados no mesmo efeito fixo espúrio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panel identifier for use in fixed effects (feols(... | id_panel)). Equal to id_rs3 when matching succeeded (panel_matched==1); when id_rs3 is NA, assigned a unique row-level ID (prefix 'unmatched_'), so different unmatched individuals are not lumped into the same spurious fixed effect.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">String. Equals id_rs3 for matched rows; 'unmatched_&lt;row number&gt;' for unmatched rows. Always non-missing — safe to use directly as the FE variable in feols().</t>
-  </si>
-  <si>
-    <t xml:space="preserve">panel_matched</t>
-  </si>
-  <si>
     <t xml:space="preserve">=1 se id_rs3 não é NA, ou seja, se o indivíduo foi pareado com sucesso entre trimestres pelo algoritmo Estágio 3 (Teoria dos Grafos). =0 caso contrário (id_panel é um ID único por linha).</t>
   </si>
   <si>
@@ -390,10 +390,10 @@
     <t xml:space="preserve">VD4009</t>
   </si>
   <si>
-    <t xml:space="preserve">Posição na ocupação no trabalho principal (1=empregado com carteira privado, 2=empregado sem carteira privado, 3=empregado com carteira público, 4=empregado sem carteira público, 5=militar e servidor estatutário, 6=sem carteira doméstico, 7=com carteira doméstico, 8=empregador, 9=conta própria, 10=trabalhador familiar auxiliar)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Position in main job (1=private employee with formal contract, 2=private employee without formal contract, 3=public employee with formal contract, 4=public employee without formal contract, 5=military/civil servant, 6=domestic worker without contract, 7=domestic worker with contract, 8=employer, 9=self-employed, 10=unpaid family worker)</t>
+    <t xml:space="preserve">Posição na ocupação no trabalho principal (1=empregado privado com carteira, 2=empregado privado sem carteira, 3=trabalhador doméstico com carteira, 4=trabalhador doméstico sem carteira, 5=empregado público com carteira, 6=empregado público sem carteira, 7=militar e servidor estatutário, 8=empregador, 9=conta-própria, 10=trabalhador familiar auxiliar). clt_private = (VD4009==1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position in main job (1=private employee with signed card, 2=private employee without signed card, 3=domestic worker with signed card, 4=domestic worker without signed card, 5=public employee with signed card, 6=public employee without signed card, 7=military/statutory servant, 8=employer, 9=self-employed, 10=unpaid family worker). clt_private = (VD4009==1).</t>
   </si>
   <si>
     <t xml:space="preserve">1–10. See description for category labels.</t>
@@ -423,19 +423,55 @@
     <t xml:space="preserve">formal</t>
   </si>
   <si>
-    <t xml:space="preserve">Emprego formal (com carteira assinada, servidor público ou militar)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formal employment (signed labor card, civil servant, or military)</t>
+    <t xml:space="preserve">Emprego formal. =1 inclui: empregados com carteira (privado, doméstico, público), militares/estatutários, E conta própria (VD4009=9) que contribui para a previdência (INSS). Empregadores (VD4009=8) ficam como nem formal nem informal (formal=0 e informal=0), logo formal+informal != 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formal employment. =1 includes: employees with a signed card (private, domestic, public), military/statutory servants, AND self-employed (conta própria, VD4009=9) who contribute to social security (INSS). Employers (VD4009=8) are classified as neither formal nor informal (formal=0 and informal=0), so formal+informal != 1.</t>
   </si>
   <si>
     <t xml:space="preserve">informal</t>
   </si>
   <si>
-    <t xml:space="preserve">Emprego informal (sem carteira, conta própria sem contribuição)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Informal employment (no contract, self-employed without social security contribution)</t>
+    <t xml:space="preserve">Emprego informal (empregado sem carteira, doméstico/público sem carteira, conta própria sem contribuição ao INSS, trabalhador familiar auxiliar). Empregadores não entram aqui.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informal employment (employee without a signed card, domestic/public without a card, self-employed not contributing to INSS, unpaid family worker). Employers are not included here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in_labor_force</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador de participação na força de trabalho (= forca_trab) como inteiro 0/1 sobre toda a amostra. Variável de desfecho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor force participation indicator (= forca_trab) as a clean 0/1 integer over all sample women. Outcome variable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 or 1 (integer). = forca_trab; never NA over the sample.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">employed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador de ocupação sobre TODA a amostra: =1 se na força de trabalho E ocupada, caso contrário 0 (fora da força de trabalho → 0). Usar esta, não `ocupado`, para o desfecho de emprego e taxas de emprego incondicionais.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employment indicator over the FULL sample: =1 if in the labor force AND occupied, else 0 (out-of-labor-force → 0). Use this, not `ocupado`, for the employment outcome and unconditional employment rates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 or 1 (integer) over all sample women. Out-of-labor-force coded 0. Preferred employment outcome (`ocupado` is NA out of the labor force).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unemployed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador de desemprego sobre TODA a amostra: =1 se na força de trabalho E não ocupada (desocupada), caso contrário 0. Variável de desfecho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment indicator over the FULL sample: =1 if in the labor force AND not occupied (desocupado), else 0. Outcome variable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 or 1 (integer) over all sample women. In labor force and not occupied (desocupada).</t>
   </si>
   <si>
     <t xml:space="preserve">VD4019</t>
@@ -498,10 +534,10 @@
     <t xml:space="preserve">V4022</t>
   </si>
   <si>
-    <t xml:space="preserve">Local de trabalho (1=estabelecimento do empregador, 2=estabelecimento de cliente/terceiro, 3=veículo, 4=domicílio próprio com local fixo, 5=domicílio próprio sem local fixo, 6=área externa/logradouro). Disponível a partir de 2018T1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work location (1=employer premises, 2=client/other premises, 3=vehicle, 4=own home with dedicated workspace, 5=own home without dedicated workspace, 6=outdoors/street). Available from Q1 2018.</t>
+    <t xml:space="preserve">Local de trabalho (1=estabelecimento de outro negócio/empresa, 2=local designado pelo empregador/cliente/freguês, 3=domicílio de empregador/patrão/sócio/freguês, 4=domicílio de residência em local exclusivo para a atividade, 5=domicílio de residência sem local exclusivo, 6=veículo automotor, 7=via ou área pública, 8=outro local). home_office = V4022 ∈ {4,5}. Disponível a partir de 2018T1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work location (1=another business/firm's premises, 2=location designated by employer/client, 3=home of employer/partner/client, 4=own residence with a dedicated workspace, 5=own residence without a dedicated workspace, 6=motor vehicle, 7=public way/area, 8=other). home_office = V4022 ∈ {4,5}. Available from Q1 2018.</t>
   </si>
   <si>
     <t xml:space="preserve">1–6. NA before Q1 2018. Key values: 4 and 5 = telework/home office.</t>
@@ -772,6 +808,18 @@
   </si>
   <si>
     <t xml:space="preserve">0 or 1 (integer). Use in robustness specifications alongside post_mp_alt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clt_private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=1 se VD4009==1 (empregado no setor privado com carteira = empregado CLT). Grupo em que o Art. 75-F de fato vincula. Usado como corte de placebo/heterogeneidade (não como restrição amostral). =0 para os demais, inclusive não ocupadas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=1 if VD4009==1 (private-sector employee with a signed card = CLT employee). The group Art. 75-F actually binds on. Used as a placebo/heterogeneity split (not a sample restriction). =0 otherwise, including the non-employed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 or 1 (integer). Sharp CLT (private carteira) indicator, VD4009==1. Heterogeneity/placebo moderator; ~19.5% of sample women, ~34% of employed.</t>
   </si>
   <si>
     <t xml:space="preserve">Color</t>
@@ -1235,22 +1283,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1259,30 +1307,30 @@
         <v>23</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>29</v>
@@ -1302,7 +1350,7 @@
         <v>33</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>34</v>
@@ -1322,7 +1370,7 @@
         <v>33</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>38</v>
@@ -1339,10 +1387,10 @@
         <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>42</v>
@@ -1362,7 +1410,7 @@
         <v>33</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>46</v>
@@ -1382,7 +1430,7 @@
         <v>33</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>50</v>
@@ -1422,7 +1470,7 @@
         <v>33</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>58</v>
@@ -1442,7 +1490,7 @@
         <v>33</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>62</v>
@@ -1482,7 +1530,7 @@
         <v>33</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>71</v>
@@ -1502,7 +1550,7 @@
         <v>33</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>75</v>
@@ -1522,7 +1570,7 @@
         <v>33</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>79</v>
@@ -1542,7 +1590,7 @@
         <v>33</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>83</v>
@@ -1562,7 +1610,7 @@
         <v>33</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>87</v>
@@ -1582,7 +1630,7 @@
         <v>33</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>91</v>
@@ -1662,7 +1710,7 @@
         <v>33</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>107</v>
@@ -1682,7 +1730,7 @@
         <v>33</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>111</v>
@@ -1722,7 +1770,7 @@
         <v>33</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>119</v>
@@ -1742,7 +1790,7 @@
         <v>33</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>122</v>
@@ -1762,7 +1810,7 @@
         <v>33</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>125</v>
@@ -1782,7 +1830,7 @@
         <v>13</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>129</v>
@@ -1802,7 +1850,7 @@
         <v>13</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>133</v>
@@ -1822,7 +1870,7 @@
         <v>13</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>136</v>
@@ -1842,7 +1890,7 @@
         <v>13</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>139</v>
@@ -1855,62 +1903,62 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D34" s="4" t="s">
+      <c r="B34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="3" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="B35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="3" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D36" s="2" t="s">
+      <c r="B36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="3" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1931,12 +1979,12 @@
         <v>155</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>33</v>
@@ -1945,53 +1993,53 @@
         <v>66</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="4" t="s">
+      <c r="A39" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="B39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="E39" s="2" t="s">
         <v>163</v>
       </c>
+      <c r="F39" s="2" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="A40" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="B40" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="E40" s="4" t="s">
         <v>167</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="41">
@@ -2002,7 +2050,7 @@
         <v>33</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>169</v>
@@ -2022,7 +2070,7 @@
         <v>33</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>173</v>
@@ -2042,7 +2090,7 @@
         <v>13</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>177</v>
@@ -2055,22 +2103,22 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="B44" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="4" t="s">
         <v>183</v>
       </c>
     </row>
@@ -2082,7 +2130,7 @@
         <v>33</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>185</v>
@@ -2095,103 +2143,103 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="3" t="s">
+      <c r="B46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="F46" s="2" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D47" s="3" t="s">
+      <c r="B47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>131</v>
+      <c r="F47" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="3" t="s">
+      <c r="A48" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="B48" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="E48" s="4" t="s">
         <v>198</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>206</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51">
@@ -2199,10 +2247,10 @@
         <v>207</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>208</v>
@@ -2219,10 +2267,10 @@
         <v>211</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>212</v>
@@ -2239,10 +2287,10 @@
         <v>215</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>216</v>
@@ -2259,10 +2307,10 @@
         <v>219</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>220</v>
@@ -2279,10 +2327,10 @@
         <v>223</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>224</v>
@@ -2291,87 +2339,87 @@
         <v>225</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="D58" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="60">
@@ -2379,10 +2427,10 @@
         <v>241</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>242</v>
@@ -2399,10 +2447,10 @@
         <v>245</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>246</v>
@@ -2419,10 +2467,10 @@
         <v>249</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>250</v>
@@ -2432,6 +2480,86 @@
       </c>
       <c r="F62" s="3" t="s">
         <v>252</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -2455,10 +2583,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2">
@@ -2466,10 +2594,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3">
@@ -2477,21 +2605,21 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary/variable_dictionary.xlsx
+++ b/dictionary/variable_dictionary.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="281">
   <si>
     <t xml:space="preserve">Variable Name</t>
   </si>
@@ -820,6 +820,18 @@
   </si>
   <si>
     <t xml:space="preserve">0 or 1 (integer). Sharp CLT (private carteira) indicator, VD4009==1. Heterogeneity/placebo moderator; ~19.5% of sample women, ~34% of employed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_youngest_child_any</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idade do filho mais novo de QUALQUER idade no domicílio (todos os tipos de filho; NA se não há filhos). Subsume as definições de grupo: tratado = (≤4); janela de controle [5,K]; Controle B = (≥8 ou NA). Usada na robustez de janela de controle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age of the youngest child of ANY age in the household (all child types; NA if no children). Subsumes the group definitions: treated = (&lt;=4); control window [5,K]; Control B = (&gt;=8 or NA). Used for the control-window robustness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integer years (0-17+) or NA. Youngest child of any age. Treated == (value &lt;= 4); control window [5,K] == (value in 5:K).</t>
   </si>
   <si>
     <t xml:space="preserve">Color</t>
@@ -2562,6 +2574,26 @@
         <v>268</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -2583,10 +2615,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2">
@@ -2594,10 +2626,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3">
@@ -2605,10 +2637,10 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4">
@@ -2616,10 +2648,10 @@
         <v>19</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary/variable_dictionary.xlsx
+++ b/dictionary/variable_dictionary.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
   <si>
     <t xml:space="preserve">Variable Name</t>
   </si>
@@ -342,7 +342,7 @@
     <t xml:space="preserve">Highest level of education attended or completed (1–7 scale)</t>
   </si>
   <si>
-    <t xml:space="preserve">1=No schooling, 2=Incomplete primary (4-year), 3=Complete primary (4-year) or incomplete (8-year), 4=Complete primary (8-year) or incomplete secondary, 5=Complete secondary or incomplete higher, 6=Complete higher, 7=Postgraduate</t>
+    <t xml:space="preserve">1=No schooling (&lt;1 year), 2=Incomplete fundamental, 3=Complete fundamental, 4=Incomplete secondary, 5=Complete secondary, 6=Incomplete higher, 7=Complete higher (Superior completo). higher_educ = (VD3004==7).</t>
   </si>
   <si>
     <t xml:space="preserve">VD3005</t>
@@ -832,6 +832,30 @@
   </si>
   <si>
     <t xml:space="preserve">Integer years (0-17+) or NA. Youngest child of any age. Treated == (value &lt;= 4); control window [5,K] == (value in 5:K).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador de sexo feminino (=1 se V2007==2). A base contém ambos os sexos; as análises principais filtram female==1. Homens entram apenas no triple-difference (DDD) e no placebo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Female indicator (=1 if V2007==2). The base holds both sexes; main analyses filter female==1. Men enter only the triple-difference (DDD) and the placebo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 or 1 (integer). V2007: 1=male, 2=female.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">higher_educ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensino superior completo (=1 se VD3004==7). Split de educação mais interpretável que faixa_educ, usado na heterogeneidade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completed higher education (=1 if VD3004==7). More interpretable education split than faixa_educ, used in the heterogeneity analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 or 1 (integer). VD3004==7 (Superior completo). ~19.7% of women.</t>
   </si>
   <si>
     <t xml:space="preserve">Color</t>
@@ -2594,6 +2618,46 @@
         <v>272</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -2615,10 +2679,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2">
@@ -2626,10 +2690,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3">
@@ -2637,10 +2701,10 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4">
@@ -2648,10 +2712,10 @@
         <v>19</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary/variable_dictionary.xlsx
+++ b/dictionary/variable_dictionary.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Survey year</t>
   </si>
   <si>
-    <t xml:space="preserve">2018–2025</t>
+    <t xml:space="preserve">2018–2026</t>
   </si>
   <si>
     <t xml:space="preserve">Trimestre</t>
@@ -147,7 +147,7 @@
     <t xml:space="preserve">Numeric time identifier (Year × 10 + Quarter). E.g. 20221 = Q1 2022</t>
   </si>
   <si>
-    <t xml:space="preserve">E.g. 20181 (Q1 2018) through 20254 (Q4 2025)</t>
+    <t xml:space="preserve">E.g. 20181 (Q1 2018) through 20261 (Q1 2026)</t>
   </si>
   <si>
     <t xml:space="preserve">V1016</t>
@@ -207,7 +207,7 @@
     <t xml:space="preserve">Panel rotation group (panels 6 to 13 in the available data)</t>
   </si>
   <si>
-    <t xml:space="preserve">6–13 in this dataset (2018–2025)</t>
+    <t xml:space="preserve">6–13 in this dataset (2018–2026)</t>
   </si>
   <si>
     <t xml:space="preserve">V1028</t>
@@ -282,7 +282,7 @@
     <t xml:space="preserve">Position in household. PNADC codes: 01=household head, 02=spouse/partner (different sex), 03=spouse/partner (same sex), 04=child of BOTH head and spouse/partner, 05=child of head ONLY, 06=stepchild, 07=son/daughter-in-law, 08=parent/stepparent of head, 09=parent-in-law, 10=grandchild, 11=great-grandchild, 12=sibling, 13=grandparent, 14=other relative, 15=non-relative member (does not share expenses), 16=non-relative member (shares expenses), 17=lodger, 18=domestic worker, 19=domestic worker's relative. NOTE: grandchild (10) and great-grandchild (11) are SEPARATE codes, not combined.</t>
   </si>
   <si>
-    <t xml:space="preserve">1–13. Key values for this project: 1 (head), 2–3 (spouse), 4–6 (child), 10 (grandchild).</t>
+    <t xml:space="preserve">1–19. Key values for this project: 1 (head), 2–3 (spouse), 4–6 (child/stepchild), 10–11 (grandchild/great-grandchild).</t>
   </si>
   <si>
     <t xml:space="preserve">V1022</t>

--- a/dictionary/variable_dictionary.xlsx
+++ b/dictionary/variable_dictionary.xlsx
@@ -492,13 +492,13 @@
     <t xml:space="preserve">Deflator do rendimento habitual (IBGE, base trimestral)</t>
   </si>
   <si>
-    <t xml:space="preserve">Habitual income deflator (IBGE, quarterly base)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real number between 0 and 1. Multiply by VD4019 to get real income.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rendimento_habitual_real</t>
+    <t xml:space="preserve">Habitual earnings deflator (IBGE, quarterly base)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real number between 0 and 1. Multiply by VD4019 to get real earnings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">earnings_habitual_real</t>
   </si>
   <si>
     <t xml:space="preserve">Rendimento mensal habitual real de todos os trabalhos (VD4019 × Habitual, em R$)</t>
@@ -507,7 +507,7 @@
     <t xml:space="preserve">Real habitual monthly earnings from all jobs (VD4019 × Habitual, in R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">Positive real or NA. Main income variable for analysis.</t>
+    <t xml:space="preserve">Positive real or NA. Main earnings variable for analysis.</t>
   </si>
   <si>
     <t xml:space="preserve">VD4031</t>

--- a/dictionary/variable_dictionary.xlsx
+++ b/dictionary/variable_dictionary.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
   <si>
     <t xml:space="preserve">Variable Name</t>
   </si>
@@ -856,6 +856,30 @@
   </si>
   <si>
     <t xml:space="preserve">0 or 1 (integer). VD3004==7 (Superior completo). ~19.7% of women.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_youngest_child_months_any</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idade em MESES da criança mais nova de qualquer idade no domicílio, reconstruída do mês/ano de nascimento (V20081/V20082) e avaliada no ponto médio do trimestre de referência (a data exata da entrevista não é divulgada; o dia de nascimento V2008 não é usado). Contínua; usada na robustez de corte etário por data de nascimento em 06_robustness.R (teto de 48/49/51/53/60 meses). NA (~7% das crianças &lt;4) quando a data de nascimento da criança mais nova é inutilizável. Apenas robustez — a especificação principal usa idade em anos completos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age IN MONTHS of the youngest child of any age in the household, reconstructed from birth month/year (V20081/V20082) and evaluated at the reference-quarter midpoint (the exact interview date is not released; the day of birth V2008 is not used). Continuous; used in the exact-birthdate age-cutoff robustness in 06_robustness.R (ceiling 48/49/51/53/60 months). NA (~7% of under-4 children) when the youngest child's birth date is unusable. Robustness only — the main specification uses completed-year age.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-negative integer (months) or NA. Treated at ceiling C == (value &lt; C); comparison held at Control A == (value in [60, 96)). NA when youngest child's DOB unusable (~7% of under-4 children).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">single_mother</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=1 se mulher chefe do domicílio (V2005==1) sem cônjuge/companheiro(a) co-residente (nenhum membro com V2005 ∈ {2,3}; PNADC trimestral não traz estado civil). No sample de análise (que condiciona à presença de criança pequena) identifica a mãe solteira/sem parceiro co-residente. Usada apenas como moderadora de heterogeneidade (baseline), nunca como restrição.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=1 if a female household head (V2005==1) with no co-resident spouse or partner (no household member with V2005 in {2,3}; the quarterly PNADC carries no marital-status variable). In the analysis sample, which conditions on the presence of a young child, this identifies the single (lone) mother — a mother with no co-resident partner. Used only as a baseline heterogeneity moderator, never as a sample restriction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 or 1 (integer). =1 for a female lone household head (no co-resident partner). Baseline heterogeneity moderator (single vs. partnered mother); ~1/4 of treated women in the sample.</t>
   </si>
   <si>
     <t xml:space="preserve">Color</t>
@@ -2658,6 +2682,46 @@
         <v>280</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -2679,10 +2743,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2">
@@ -2690,10 +2754,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3">
@@ -2701,10 +2765,10 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4">
@@ -2712,10 +2776,10 @@
         <v>19</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary/variable_dictionary.xlsx
+++ b/dictionary/variable_dictionary.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="308">
   <si>
     <t xml:space="preserve">Variable Name</t>
   </si>
@@ -672,6 +672,18 @@
     <t xml:space="preserve">0 or 1 (integer). Robustness: V2005 ∈ {4,5,10,11}, age ≤4. Excludes stepchildren.</t>
   </si>
   <si>
+    <t xml:space="preserve">has_child_u4_no_gc_sc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=1 se is_head_or_spouse==1 e há criança ≤4 anos no domicílio, excluindo netos(as)/bisnetos(as) E enteados(as) (V2005 ∈ {10,11,6}). Inclui apenas filhos(as) biológicos/adotivos do responsável e/ou cônjuge (V2005=4,5). Versão de robustez.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=1 if is_head_or_spouse==1 and household has a child aged ≤4, excluding both grandchildren/great-grandchildren AND stepchildren (V2005 ∈ {10,11,6}). Includes only biological children of head and/or spouse (V2005=4,5). Robustness version.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 or 1 (integer). Robustness: V2005 ∈ {4,5}, age ≤4. Excludes both grandchildren/great-grandchildren and stepchildren.</t>
+  </si>
+  <si>
     <t xml:space="preserve">has_child_5_7</t>
   </si>
   <si>
@@ -708,6 +720,18 @@
     <t xml:space="preserve">0 or 1 (integer). Robustness Control A: V2005 ∈ {4,5,10,11}, age 5–7. Excludes stepchildren.</t>
   </si>
   <si>
+    <t xml:space="preserve">has_child_5_7_no_gc_sc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=1 se is_head_or_spouse==1 e há criança de 5 a 7 anos no domicílio, excluindo netos(as)/bisnetos(as) E enteados(as) (V2005 ∈ {4,5} apenas). Versão de robustez do Controle A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=1 if is_head_or_spouse==1 and household has a child aged 5–7, excluding both grandchildren/great-grandchildren and stepchildren (V2005 ∈ {4,5} only). Robustness version of Control A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 or 1 (integer). Robustness Control A: V2005 ∈ {4,5}, age 5–7. Excludes both grandchildren/great-grandchildren and stepchildren.</t>
+  </si>
+  <si>
     <t xml:space="preserve">age_youngest_child</t>
   </si>
   <si>
@@ -736,6 +760,15 @@
   </si>
   <si>
     <t xml:space="preserve">Age of youngest child aged ≤4, excluding stepchildren (NA if has_child_u4_no_sc==0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_youngest_child_no_gc_sc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idade da criança mais nova ≤4 anos no domicílio, excluindo netos/bisnetos E enteados (NA se has_child_u4_no_gc_sc==0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age of youngest child aged ≤4, excluding both grandchildren/great-grandchildren and stepchildren (NA if has_child_u4_no_gc_sc==0)</t>
   </si>
   <si>
     <t xml:space="preserve">potential_telework</t>
@@ -2430,7 +2463,7 @@
         <v>19</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>232</v>
@@ -2450,7 +2483,7 @@
         <v>19</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>236</v>
@@ -2459,12 +2492,12 @@
         <v>237</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>19</v>
@@ -2473,53 +2506,53 @@
         <v>66</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="D60" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F60" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="62">
@@ -2530,7 +2563,7 @@
         <v>19</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>250</v>
@@ -2539,187 +2572,247 @@
         <v>251</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D63" s="3" t="s">
+      <c r="E63" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="F63" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D64" s="3" t="s">
+      <c r="E64" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="F64" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D65" s="3" t="s">
+      <c r="E65" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="F65" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D66" s="3" t="s">
+      <c r="E66" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="F66" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D67" s="3" t="s">
+      <c r="E67" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="F67" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D68" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="F68" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D69" s="3" t="s">
+      <c r="E69" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="F69" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D70" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="F70" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D71" s="3" t="s">
+      <c r="E71" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="F71" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="F71" s="3" t="s">
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
         <v>288</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -2743,10 +2836,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2">
@@ -2754,10 +2847,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3">
@@ -2765,10 +2858,10 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4">
@@ -2776,10 +2869,10 @@
         <v>19</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary/variable_dictionary.xlsx
+++ b/dictionary/variable_dictionary.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="320">
   <si>
     <t xml:space="preserve">Variable Name</t>
   </si>
@@ -913,6 +913,42 @@
   </si>
   <si>
     <t xml:space="preserve">0 or 1 (integer). =1 for a female lone household head (no co-resident partner). Baseline heterogeneity moderator (single vs. partnered mother); ~1/4 of treated women in the sample.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dia de nascimento da própria pessoa entrevistada (a pessoa da linha). Variável bruta da PNADC. NÃO é a data de nascimento da criança: age_youngest_child_months_any usa o V20081/V20082 da criança mais nova do domicílio, obtidos do roster durante o build. O dia de nascimento não alimenta nenhuma variável derivada (a data exata da entrevista não é divulgada, tornando precisão sub-mensal espúria).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day of birth of the interviewed person (the row's person). Raw PNADC variable. This is NOT the child's date of birth: age_youngest_child_months_any uses the youngest child's V20081/V20082, pulled from the household roster during the build. The day of birth feeds no derived variable (the exact interview date is not released, making sub-monthly precision spurious).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1–31 (integer) or NA. Interviewed person's own day of birth.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V20081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mês de nascimento da própria pessoa entrevistada (variável bruta da PNADC). É o V20081 da criança mais nova do domicílio (não este, que é o da pessoa da linha) que é usado no build para construir age_youngest_child_months_any.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Month of birth of the interviewed person (raw PNADC variable). It is the youngest child's V20081 in the household (not this one, which is the row person's) that is used in the build to construct age_youngest_child_months_any.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1–12 (integer) or NA. Interviewed person's own month of birth.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V20082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ano de nascimento da própria pessoa entrevistada (variável bruta da PNADC). É o V20082 da criança mais nova do domicílio que é usado no build para construir age_youngest_child_months_any.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year of birth of the interviewed person (raw PNADC variable). It is the youngest child's V20082 in the household that is used in the build to construct age_youngest_child_months_any.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four-digit year or NA. Interviewed person's own year of birth (roughly 1968–2008 in this sample of persons aged 18–49 across 2018–2026).</t>
   </si>
   <si>
     <t xml:space="preserve">Color</t>
@@ -2815,6 +2851,66 @@
         <v>299</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>311</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -2836,10 +2932,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2">
@@ -2847,10 +2943,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3">
@@ -2858,10 +2954,10 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4">
@@ -2869,10 +2965,10 @@
         <v>19</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary/variable_dictionary.xlsx
+++ b/dictionary/variable_dictionary.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="324">
   <si>
     <t xml:space="preserve">Variable Name</t>
   </si>
@@ -846,13 +846,13 @@
     <t xml:space="preserve">clt_private</t>
   </si>
   <si>
-    <t xml:space="preserve">=1 se VD4009==1 (empregado no setor privado com carteira = empregado CLT). Grupo em que o Art. 75-F de fato vincula. Usado como corte de placebo/heterogeneidade (não como restrição amostral). =0 para os demais, inclusive não ocupadas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">=1 if VD4009==1 (private-sector employee with a signed card = CLT employee). The group Art. 75-F actually binds on. Used as a placebo/heterogeneity split (not a sample restriction). =0 otherwise, including the non-employed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 or 1 (integer). Sharp CLT (private carteira) indicator, VD4009==1. Heterogeneity/placebo moderator; ~19.5% of sample women, ~34% of employed.</t>
+    <t xml:space="preserve">=1 se VD4009==1 (empregado no setor privado com carteira = empregado CLT privado). NOTA: substituído por clt_covered (VD4009 ∈ {1,5}, que inclui os celetistas do setor público) como grupo 'coberto' principal; mantido como corte de robustez (setor privado apenas). Corte de placebo/heterogeneidade, não restrição amostral. =0 para os demais, inclusive não ocupadas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=1 if VD4009==1 (private-sector employee with a signed card = private CLT employee). NOTE: superseded by clt_covered (VD4009 ∈ {1,5}, which adds public-sector celetistas) as the headline covered group; kept as the private-only robustness split. Placebo/heterogeneity moderator, not a sample restriction. =0 otherwise, including the non-employed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 or 1 (integer). Private-only CLT (carteira) indicator, VD4009==1. Narrower robustness split; see clt_covered for the full covered group (private + public celetistas). ~19.5% of sample women, ~34% of employed.</t>
   </si>
   <si>
     <t xml:space="preserve">age_youngest_child_any</t>
@@ -949,6 +949,18 @@
   </si>
   <si>
     <t xml:space="preserve">Four-digit year or NA. Interviewed person's own year of birth (roughly 1968–2008 in this sample of persons aged 18–49 across 2018–2026).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clt_covered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=1 se VD4009 ∈ {1,5} (empregado com carteira assinada no setor privado OU público). Grupo efetivamente coberto pelo Art. 75-F: empregados celetistas privados E celetistas de empresas públicas/sociedades de economia mista (Banco do Brasil, Caixa, Petrobras, Correios), que são contratados sob o regime da CLT. Exclui servidores estatutários (VD4009==7), domésticos (VD4009==3), informais e conta-própria. Substitui clt_private como grupo 'coberto' principal (clt_private = VD4009==1 fica como robustez). =0 para os demais, inclusive não ocupadas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=1 if VD4009 ∈ {1,5} (signed-card employee in the private OR public sector). The group actually covered by Art. 75-F: private-sector celetistas AND the celetistas of public companies / mixed-economy firms (Banco do Brasil, Caixa, Petrobras, the postal service), who are hired under the CLT regime. Excludes statutory servants (VD4009==7), domestic workers (VD4009==3), the informal, and the self-employed. Supersedes clt_private as the headline 'legally covered' group (clt_private = VD4009==1 is kept as a robustness split). =0 otherwise, including the non-employed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 or 1 (integer). Covered-CLT indicator, VD4009 ∈ {1,5} (private + public celetistas). Headline 'legally covered' group for Art. 75-F; public celetistas ≈4.8% of the covered pool among treated women. clt_private (VD4009==1) is the narrower private-only robustness split.</t>
   </si>
   <si>
     <t xml:space="preserve">Color</t>
@@ -2911,6 +2923,26 @@
         <v>311</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -2932,10 +2964,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2">
@@ -2943,10 +2975,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3">
@@ -2954,10 +2986,10 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4">
@@ -2965,10 +2997,10 @@
         <v>19</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary/variable_dictionary.xlsx
+++ b/dictionary/variable_dictionary.xlsx
@@ -849,10 +849,10 @@
     <t xml:space="preserve">=1 se VD4009==1 (empregado no setor privado com carteira = empregado CLT privado). NOTA: substituído por clt_covered (VD4009 ∈ {1,5}, que inclui os celetistas do setor público) como grupo 'coberto' principal; mantido como corte de robustez (setor privado apenas). Corte de placebo/heterogeneidade, não restrição amostral. =0 para os demais, inclusive não ocupadas.</t>
   </si>
   <si>
-    <t xml:space="preserve">=1 if VD4009==1 (private-sector employee with a signed card = private CLT employee). NOTE: superseded by clt_covered (VD4009 ∈ {1,5}, which adds public-sector celetistas) as the headline covered group; kept as the private-only robustness split. Placebo/heterogeneity moderator, not a sample restriction. =0 otherwise, including the non-employed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 or 1 (integer). Private-only CLT (carteira) indicator, VD4009==1. Narrower robustness split; see clt_covered for the full covered group (private + public celetistas). ~19.5% of sample women, ~34% of employed.</t>
+    <t xml:space="preserve">=1 if VD4009==1 (private-sector employee with a signed card = private CLT employee). NOTE: superseded by clt_covered (VD4009 ∈ {1,5}, which adds public-sector celetistas) as the covered group. clt_private is derived in the build but is not used in the current analysis, which uses clt_covered throughout. =0 otherwise, including the non-employed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 or 1 (integer). Private-only CLT (carteira) indicator, VD4009==1. Narrower private-only definition, superseded by clt_covered and not used in the current analysis; see clt_covered for the full covered group (private + public celetistas). ~19.5% of sample women, ~34% of employed.</t>
   </si>
   <si>
     <t xml:space="preserve">age_youngest_child_any</t>
@@ -957,10 +957,10 @@
     <t xml:space="preserve">=1 se VD4009 ∈ {1,5} (empregado com carteira assinada no setor privado OU público). Grupo efetivamente coberto pelo Art. 75-F: empregados celetistas privados E celetistas de empresas públicas/sociedades de economia mista (Banco do Brasil, Caixa, Petrobras, Correios), que são contratados sob o regime da CLT. Exclui servidores estatutários (VD4009==7), domésticos (VD4009==3), informais e conta-própria. Substitui clt_private como grupo 'coberto' principal (clt_private = VD4009==1 fica como robustez). =0 para os demais, inclusive não ocupadas.</t>
   </si>
   <si>
-    <t xml:space="preserve">=1 if VD4009 ∈ {1,5} (signed-card employee in the private OR public sector). The group actually covered by Art. 75-F: private-sector celetistas AND the celetistas of public companies / mixed-economy firms (Banco do Brasil, Caixa, Petrobras, the postal service), who are hired under the CLT regime. Excludes statutory servants (VD4009==7), domestic workers (VD4009==3), the informal, and the self-employed. Supersedes clt_private as the headline 'legally covered' group (clt_private = VD4009==1 is kept as a robustness split). =0 otherwise, including the non-employed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 or 1 (integer). Covered-CLT indicator, VD4009 ∈ {1,5} (private + public celetistas). Headline 'legally covered' group for Art. 75-F; public celetistas ≈4.8% of the covered pool among treated women. clt_private (VD4009==1) is the narrower private-only robustness split.</t>
+    <t xml:space="preserve">=1 if VD4009 ∈ {1,5} (signed-card employee in the private OR public sector). The group actually covered by Art. 75-F: private-sector celetistas AND the celetistas of public companies / mixed-economy firms (Banco do Brasil, Caixa, Petrobras, the postal service), who are hired under the CLT regime. Excludes statutory servants (VD4009==7), domestic workers (VD4009==3), the informal, and the self-employed. Supersedes clt_private as the headline 'legally covered' group (clt_private = VD4009==1 is the narrower private-only definition, not used in the current analysis). =0 otherwise, including the non-employed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 or 1 (integer). Covered-CLT indicator, VD4009 ∈ {1,5} (private + public celetistas). Headline 'legally covered' group for Art. 75-F; public celetistas ≈4.8% of the covered pool among treated women. clt_private (VD4009==1) is the narrower private-only definition, not used in the current analysis.</t>
   </si>
   <si>
     <t xml:space="preserve">Color</t>
